--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487132_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487132_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4612</v>
+        <v>7.0284</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5981</v>
+        <v>3.2775</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8631</v>
+        <v>3.751</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6259</v>
+        <v>3.2623</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6041</v>
+        <v>1.7221</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9782</v>
+        <v>1.5401</v>
       </c>
       <c r="J2" t="n">
-        <v>2.921</v>
+        <v>2.5277</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9131</v>
+        <v>1.9093</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2951</v>
+        <v>0.7346</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3091</v>
+        <v>-0.1872</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9861</v>
+        <v>0.9218</v>
       </c>
       <c r="P2" t="n">
-        <v>0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4741</v>
+        <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5145</v>
+        <v>0.1897</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8304</v>
+        <v>0.0684</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6841</v>
+        <v>0.1213</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7418</v>
+        <v>4.5415</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7418</v>
+        <v>4.5415</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8896</v>
+        <v>5.5833</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0584</v>
+        <v>4.0147</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8313</v>
+        <v>1.5686</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2623</v>
+        <v>0.6259</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7221</v>
+        <v>1.6041</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5401</v>
+        <v>-0.9782</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5277</v>
+        <v>2.921</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9093</v>
+        <v>2.9131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7346</v>
+        <v>-2.2951</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1872</v>
+        <v>-1.3091</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9218</v>
+        <v>-0.9861</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8951</v>
+        <v>3.4741</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0509</v>
+        <v>1.6366</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1507</v>
+        <v>1.247</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2016</v>
+        <v>0.3896</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5415</v>
+        <v>2.7418</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5415</v>
+        <v>2.7418</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7178</v>
+        <v>2.9004</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1722</v>
+        <v>1.4886</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5457</v>
+        <v>1.4118</v>
       </c>
       <c r="G4" t="n">
         <v>0.2993</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3836</v>
+        <v>1.5662</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6837</v>
+        <v>1.0001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7</v>
+        <v>0.5661</v>
       </c>
       <c r="V4" t="n">
         <v>1.228</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3542</v>
+        <v>1.3244</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1667</v>
+        <v>-0.0158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8125</v>
+        <v>1.3402</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9878</v>
+        <v>-1.8184</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9189</v>
+        <v>-0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9311</v>
+        <v>-1.6301</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4759</v>
+        <v>0.1099</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3131</v>
+        <v>0.9003</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1628</v>
+        <v>-0.7904</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4881</v>
+        <v>-1.9283</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3942</v>
+        <v>-1.0886</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0939</v>
+        <v>-0.8397</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7021</v>
+        <v>3.2811</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3299</v>
+        <v>0.278</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8739</v>
+        <v>0.2905</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4561</v>
+        <v>-0.0126</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5138</v>
+        <v>1.5138</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>1.5138</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4712</v>
+        <v>-0.3299</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4366</v>
+        <v>-0.4974</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9654</v>
+        <v>0.1675</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8184</v>
+        <v>-0.2418</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1883</v>
+        <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6301</v>
+        <v>-0.8318</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1099</v>
+        <v>0.2049</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9003</v>
+        <v>0.0828</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7904</v>
+        <v>0.1221</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9283</v>
+        <v>-0.4467</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0886</v>
+        <v>0.5072</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8397</v>
+        <v>-0.9539</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2811</v>
+        <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5176</v>
+        <v>0.5608</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1303</v>
+        <v>0.2628</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3874</v>
+        <v>0.2981</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5138</v>
+        <v>-1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7321</v>
+        <v>-0.3603</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4568</v>
+        <v>-1.737</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7247</v>
+        <v>1.3767</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9669</v>
@@ -1000,13 +1000,13 @@
         <v>3.0881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3047</v>
+        <v>0.6765</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5803</v>
+        <v>0.1395</v>
       </c>
       <c r="U7" t="n">
-        <v>0.885</v>
+        <v>0.537</v>
       </c>
       <c r="V7" t="n">
         <v>-1.228</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0507</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0576</v>
+        <v>-1.4076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0069</v>
+        <v>0.7589</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2418</v>
+        <v>0.9878</v>
       </c>
       <c r="H8" t="n">
-        <v>0.59</v>
+        <v>1.9189</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8318</v>
+        <v>-0.9311</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2049</v>
+        <v>2.4759</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0828</v>
+        <v>2.3131</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>0.1628</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4467</v>
+        <v>-1.4881</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5072</v>
+        <v>-0.3942</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9539</v>
+        <v>-1.0939</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>2.7021</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.16</v>
+        <v>1.0354</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2974</v>
+        <v>0.6329</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1375</v>
+        <v>0.4025</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.461</v>
+        <v>-2.1433</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0995</v>
+        <v>-1.2828</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3615</v>
+        <v>-0.8605</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4114</v>
+        <v>-1.2977</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.591</v>
+        <v>-1.0857</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8204</v>
+        <v>-0.212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1035</v>
+        <v>-0.2831</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1035</v>
+        <v>-0.2175</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5149</v>
+        <v>-1.0146</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6944</v>
+        <v>-0.8682</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8204</v>
+        <v>-0.1464</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0919</v>
+        <v>-0.5827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>-0.0347</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1461</v>
+        <v>-0.548</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8165</v>
+        <v>-2.1873</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9025</v>
+        <v>-0.7991</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.914</v>
+        <v>-1.3883</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2977</v>
+        <v>-1.4114</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0857</v>
+        <v>-0.591</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.212</v>
+        <v>-0.8204</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2831</v>
+        <v>0.1035</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2175</v>
+        <v>0.1035</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0146</v>
+        <v>-1.5149</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8682</v>
+        <v>-0.6944</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1464</v>
+        <v>-0.8204</v>
       </c>
       <c r="P10" t="n">
-        <v>0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2559</v>
+        <v>0.1818</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6544</v>
+        <v>0.0625</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6015</v>
+        <v>0.1193</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1094</v>
+        <v>-2.2012</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3093</v>
+        <v>-2.7492</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2</v>
+        <v>0.548</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4068</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6603</v>
+        <v>0.2479</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0912</v>
+        <v>0.469</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.2211</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0422</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.073500000000003</v>
+        <v>8.965800000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6003000000000003</v>
+        <v>0.2919000000000009</v>
       </c>
       <c r="F12" t="n">
-        <v>8.674099999999999</v>
+        <v>8.673900000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9677</v>
@@ -1366,7 +1366,7 @@
         <v>6.8725</v>
       </c>
       <c r="K12" t="n">
-        <v>8.682200000000002</v>
+        <v>8.6822</v>
       </c>
       <c r="L12" t="n">
         <v>-1.8098</v>
@@ -1378,7 +1378,7 @@
         <v>-4.9098</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.9304</v>
+        <v>-4.930400000000001</v>
       </c>
       <c r="P12" t="n">
         <v>1.9301</v>
@@ -1390,22 +1390,22 @@
         <v>23.1609</v>
       </c>
       <c r="S12" t="n">
-        <v>4.897899999999999</v>
+        <v>5.7902</v>
       </c>
       <c r="T12" t="n">
-        <v>3.245699999999999</v>
+        <v>4.138</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6524</v>
+        <v>1.6522</v>
       </c>
       <c r="V12" t="n">
-        <v>4.213400000000001</v>
+        <v>4.2134</v>
       </c>
       <c r="W12" t="n">
         <v>10.5123</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.299</v>
+        <v>-6.298999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6412</v>
+        <v>3.4764</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0386</v>
+        <v>1.4363</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6026</v>
+        <v>2.0401</v>
       </c>
       <c r="G13" t="n">
         <v>3.1944</v>
@@ -1468,13 +1468,13 @@
         <v>3.8602</v>
       </c>
       <c r="S13" t="n">
-        <v>2.907</v>
+        <v>0.7423</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0438</v>
+        <v>0.4416</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8632</v>
+        <v>0.3007</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3903</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5809</v>
+        <v>3.066</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4939</v>
+        <v>2.1935</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0869</v>
+        <v>0.8724</v>
       </c>
       <c r="G14" t="n">
         <v>0.5979</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4964</v>
+        <v>-0.0185</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3239</v>
+        <v>0.0235</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1725</v>
+        <v>-0.042</v>
       </c>
       <c r="V14" t="n">
         <v>1.9076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2412</v>
+        <v>0.8277</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0054</v>
+        <v>-0.5955</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2358</v>
+        <v>1.4232</v>
       </c>
       <c r="G15" t="n">
         <v>0.668</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4501</v>
+        <v>0.0367</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5764</v>
+        <v>-0.0244</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1263</v>
+        <v>0.0611</v>
       </c>
       <c r="V15" t="n">
         <v>-1.228</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5538999999999999</v>
+        <v>0.5722</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0759</v>
+        <v>-0.4899</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6298</v>
+        <v>1.0621</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2914</v>
+        <v>0.9877</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2557</v>
+        <v>0.1915</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0357</v>
+        <v>0.7961</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9564</v>
+        <v>0.4735</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3053</v>
+        <v>0.4656</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6512</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2478</v>
+        <v>0.5142</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5609</v>
+        <v>-0.2741</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6869</v>
+        <v>0.7883</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3325</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1785</v>
+        <v>0.0017</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.154</v>
+        <v>-0.5173</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7174</v>
+        <v>-0.3735</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1909</v>
+        <v>0.176</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4735</v>
+        <v>-0.5495</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9877</v>
+        <v>-0.2914</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1915</v>
+        <v>-0.2557</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7961</v>
+        <v>-0.0357</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4735</v>
+        <v>0.9564</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4656</v>
+        <v>0.3053</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.6512</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5142</v>
+        <v>-1.2478</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2741</v>
+        <v>-0.5609</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7883</v>
+        <v>-0.6869</v>
       </c>
       <c r="P17" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8052</v>
+        <v>-0.152</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6993</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1059</v>
+        <v>-0.0737</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W17" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0037</v>
+        <v>-0.6428</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.641</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1625</v>
+        <v>-0.0018</v>
       </c>
       <c r="G18" t="n">
         <v>1.3735</v>
@@ -1858,13 +1858,13 @@
         <v>2.5091</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8289</v>
+        <v>-0.468</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6544</v>
+        <v>-0.4541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1745</v>
+        <v>-0.0139</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1623</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2855</v>
+        <v>-2.3885</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6863</v>
+        <v>-1.0917</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5992</v>
+        <v>-1.2969</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3842</v>
+        <v>0.1736</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1563</v>
+        <v>-0.8539</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5405</v>
+        <v>1.0275</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5033</v>
+        <v>2.0354</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0245</v>
+        <v>0.7088</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5212</v>
+        <v>1.3267</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8875</v>
+        <v>-1.8619</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8682</v>
+        <v>-1.5627</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0193</v>
+        <v>-0.2992</v>
       </c>
       <c r="P19" t="n">
         <v>-0.965</v>
@@ -1936,28 +1936,28 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9941</v>
+        <v>-1.091</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5803</v>
+        <v>-0.232</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4138</v>
+        <v>-0.859</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9421</v>
+        <v>-0.5061</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3616</v>
+        <v>-3.0852</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9528</v>
+        <v>-2.486</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4088</v>
+        <v>-0.5992</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.052</v>
+        <v>-0.3842</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1612</v>
+        <v>0.1563</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1092</v>
+        <v>-0.5405</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1428</v>
+        <v>0.5033</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0207</v>
+        <v>1.0245</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1221</v>
+        <v>-0.5212</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1948</v>
+        <v>-0.8875</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1819</v>
+        <v>-0.8682</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0129</v>
+        <v>-0.0193</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9888</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4164</v>
+        <v>-0.38</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5724</v>
+        <v>-0.4138</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5138</v>
+        <v>-0.9421</v>
       </c>
       <c r="W20" t="n">
         <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4174</v>
+        <v>-3.3081</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6925</v>
+        <v>-0.9528</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7249</v>
+        <v>-2.3553</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1736</v>
+        <v>-1.052</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8539</v>
+        <v>-1.1612</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0275</v>
+        <v>0.1092</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0354</v>
+        <v>0.1428</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7088</v>
+        <v>0.0207</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3267</v>
+        <v>0.1221</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8619</v>
+        <v>-1.1948</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5627</v>
+        <v>-1.1819</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2992</v>
+        <v>-0.0129</v>
       </c>
       <c r="P21" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1198</v>
+        <v>-0.9353</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8328</v>
+        <v>-0.4164</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.287</v>
+        <v>-0.5189</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5061</v>
+        <v>-1.5138</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5061</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1973</v>
+        <v>-5.5501</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.9241</v>
+        <v>-6.2231</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7268</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2995</v>
@@ -2170,13 +2170,13 @@
         <v>2.8951</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6822</v>
+        <v>-1.0351</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2347</v>
+        <v>-0.5337</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4475</v>
+        <v>-0.5014</v>
       </c>
       <c r="V22" t="n">
         <v>0.6796</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.073499999999999</v>
+        <v>-7.405900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.673999999999999</v>
+        <v>-8.674199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6003999999999995</v>
+        <v>1.268</v>
       </c>
       <c r="G23" t="n">
         <v>2.968</v>
@@ -2248,19 +2248,19 @@
         <v>21.2309</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.898</v>
+        <v>-4.2304</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6523</v>
+        <v>-1.6521</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.2457</v>
+        <v>-2.5782</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.213300000000001</v>
+        <v>-4.2133</v>
       </c>
       <c r="W23" t="n">
-        <v>6.2991</v>
+        <v>6.299099999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-10.5124</v>
